--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,6 +483,41 @@
         </is>
       </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ausfall_video-upload_20260628_161739.wav</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ausfall</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ausfall</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>28.06.2026 16:17:41</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Techniker</t>
         </is>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,6 +518,41 @@
         </is>
       </c>
       <c r="G3" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260628_161930.wav</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ausfall</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>28.06.2026 16:19:31</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Techniker</t>
         </is>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,6 +553,41 @@
         </is>
       </c>
       <c r="G4" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260628_162047.wav</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ausfall</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>28.06.2026 16:20:48</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Techniker</t>
         </is>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,6 +588,41 @@
         </is>
       </c>
       <c r="G5" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260628_162203.wav</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ausfall</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>28.06.2026 16:22:04</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Techniker</t>
         </is>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,6 +623,41 @@
         </is>
       </c>
       <c r="G6" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ausfall_video-upload_20260628_172218.wav</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ausfall</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ausfall</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>28.06.2026 17:22:20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Techniker</t>
         </is>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -658,6 +658,41 @@
         </is>
       </c>
       <c r="G7" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ausfall_video-upload_20260630_181441.wav</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ausfall</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>30.06.2026 18:14:43</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Techniker</t>
         </is>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -698,6 +698,41 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_181803.wav</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>30.06.2026 18:18:04</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,6 +733,41 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_183242.wav</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>30.06.2026 18:32:43</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,6 +768,41 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_183628.wav</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>30.06.2026 18:36:29</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,41 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_183719.wav</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>30.06.2026 18:37:20</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -838,6 +838,41 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_183752.wav</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>30.06.2026 18:37:54</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,6 +873,41 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_183832.wav</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>30.06.2026 18:38:34</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -908,6 +908,41 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_183911.wav</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>30.06.2026 18:39:13</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -943,6 +943,41 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_183949.wav</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>30.06.2026 18:39:51</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -978,6 +978,41 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_184016.wav</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>30.06.2026 18:40:18</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,6 +1013,41 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_184110.wav</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>30.06.2026 18:41:12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,6 +1048,41 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_184158.wav</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>30.06.2026 18:42:00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1083,6 +1083,41 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_184257.wav</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>30.06.2026 18:42:59</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,6 +1118,41 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_184438.wav</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>30.06.2026 18:44:39</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1153,6 +1153,41 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_184639.wav</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ausfall</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>30.06.2026 18:46:41</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1188,6 +1188,41 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_184836.wav</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ausfall</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>30.06.2026 18:48:38</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1223,6 +1223,41 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_192242.wav</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ausfall</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>30.06.2026 19:22:44</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1258,6 +1258,41 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_192554.wav</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>30.06.2026 19:25:55</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1293,6 +1293,41 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260630_192709.wav</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ausfall</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>30.06.2026 19:27:11</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1328,6 +1328,41 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260705_142843.wav</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>05.07.2026 14:28:45</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1363,6 +1363,41 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260705_143129.wav</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>05.07.2026 14:31:30</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1398,6 +1398,41 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260705_143235.wav</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>05.07.2026 14:32:37</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1433,6 +1433,41 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260705_143353.wav</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>05.07.2026 14:33:54</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1468,6 +1468,41 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260705_143530.wav</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>05.07.2026 14:35:31</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1503,6 +1503,41 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260705_143659.wav</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>05.07.2026 14:37:01</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1538,6 +1538,41 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260705_143827.wav</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>05.07.2026 14:38:28</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1573,6 +1573,41 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260705_143939.wav</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>05.07.2026 14:39:40</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1608,6 +1608,41 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260705_144048.wav</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>05.07.2026 14:40:49</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1643,6 +1643,41 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260705_144134.wav</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>05.07.2026 14:41:35</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1678,6 +1678,41 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260705_144351.wav</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>05.07.2026 14:43:52</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1713,6 +1713,41 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260705_144453.wav</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>05.07.2026 14:44:54</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1748,6 +1748,41 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260705_144612.wav</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>05.07.2026 14:46:13</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,6 +1783,41 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260705_144656.wav</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>05.07.2026 14:46:57</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1818,6 +1818,41 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260705_144744.wav</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>05.07.2026 14:47:45</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1853,6 +1853,41 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_142113.wav</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:21:14</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SARPARAST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1888,6 +1888,41 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_142149.wav</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:21:51</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SARPARAST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1923,6 +1923,41 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_142343.wav</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:23:45</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SRPARAST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1958,6 +1958,41 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_142845.wav</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:28:47</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SARPARAST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1993,6 +1993,41 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_143821.wav</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:38:23</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SARPARAST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2028,6 +2028,41 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_143908.wav</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:39:10</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SARPARAST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2063,6 +2063,41 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_144131.wav</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:41:33</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SARPARAST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2098,6 +2098,41 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_144226.wav</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:42:27</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SARPARAST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2133,6 +2133,41 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_144321.wav</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:43:23</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SARPARAST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2168,6 +2168,41 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_144432.wav</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:44:33</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SARPARAST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2203,6 +2203,41 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_144520.wav</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:45:22</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SARPARAST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2238,6 +2238,41 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_144608.wav</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:46:10</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2273,6 +2273,41 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>gut_video-upload_20260706_144832.wav</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Video-Upload</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:48:33</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SARPARAST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2308,6 +2308,41 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_144924.wav</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:49:25</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SARPARAST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2343,6 +2343,41 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_145037.wav</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:50:39</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SARPARAST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2378,6 +2378,41 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_145147.wav</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:51:49</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SARPARAST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2413,6 +2413,41 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_145230.wav</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>06.07.2026 14:52:31</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SARPARAST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2448,6 +2448,41 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260706_150409.wav</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>06.07.2026 15:04:10</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>sARPrast</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2483,6 +2483,41 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>kritisch_mikrofon-live_20260707_212701.wav</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Kritisch</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Mikrofon-Live</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>07.07.2026 21:27:03</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2518,6 +2518,41 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>kritisch_datei-upload_20260707_212838.wav</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Kritisch</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>07.07.2026 21:28:39</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2553,6 +2553,41 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>kritisch_mikrofon-live_20260707_213010.wav</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kritisch</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Mikrofon-Live</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>07.07.2026 21:30:12</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2588,6 +2588,41 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ausfall_datei-upload_20260707_213257.wav</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Ausfall</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>07.07.2026 21:32:58</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2623,6 +2623,41 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>kritisch_datei-upload_20260708_142022.wav</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kritisch</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>08.07.2026 14:20:24</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2658,6 +2658,41 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>gut_datei-upload_20260708_183643.wav</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Warnung</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>08.07.2026 18:36:44</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oussama </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2693,6 +2693,41 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>warnung_datei-upload_20260708_183717.wav</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Warnung</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Warnung</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>08.07.2026 18:37:19</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oussama </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2728,6 +2728,41 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>warnung_datei-upload_20260708_183928.wav</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Warnung</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Warnung</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>08.07.2026 18:39:29</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oussama </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2763,6 +2763,41 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ausfall_datei-upload_20260708_184042.wav</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Ausfall</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>08.07.2026 18:40:43</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oussama </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2798,6 +2798,41 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>kritisch_datei-upload_20260708_184145.wav</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Kritisch</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Warnung</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>08.07.2026 18:41:46</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oussama </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2833,6 +2833,41 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ausfall_datei-upload_20260708_184247.wav</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Ausfall</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>08.07.2026 18:42:49</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oussama </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2868,6 +2868,41 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>kritisch_datei-upload_20260708_184605.wav</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Kritisch</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Warnung</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>08.07.2026 18:46:06</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oussama </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Datenbank_Uebersicht.xlsx
+++ b/Datenbank_Uebersicht.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2903,6 +2903,41 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>warnung_datei-upload_20260708_185803.wav</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Warnung</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Gut</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Datei-Upload</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>08.07.2026 18:58:05</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Techniker</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
